--- a/data/trans_dic/P37A$vacunapreferencia-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P37A$vacunapreferencia-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,38%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,09; 7,25</t>
+          <t>3,21; 7,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 4,96</t>
+          <t>1,6; 4,83</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,83; 3,43</t>
+          <t>0,74; 3,27</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,81; 13,62</t>
+          <t>7,33; 12,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,22; 5,34</t>
+          <t>1,29; 5,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,64; 4,64</t>
+          <t>0,65; 4,5</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,92; 4,28</t>
+          <t>0,9; 4,24</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>8,87; 13,65</t>
+          <t>8,82; 13,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,8; 5,64</t>
+          <t>2,85; 5,83</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,49; 3,87</t>
+          <t>1,38; 3,79</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 3,13</t>
+          <t>1,15; 3,15</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,97; 12,72</t>
+          <t>8,7; 12,27</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,33%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,84</t>
+          <t>1,07; 4,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,7; 7,4</t>
+          <t>3,0; 7,48</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,08</t>
+          <t>0,4; 3,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,59; 13,55</t>
+          <t>7,45; 13,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,91; 4,37</t>
+          <t>1,04; 4,49</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,75; 3,66</t>
+          <t>0,85; 3,72</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,14</t>
+          <t>0,55; 3,37</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,0; 10,78</t>
+          <t>5,92; 10,5</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,76</t>
+          <t>1,26; 3,79</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,26; 5,05</t>
+          <t>2,18; 5,09</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,39</t>
+          <t>0,62; 2,39</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>7,69; 11,35</t>
+          <t>7,68; 11,58</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,62; 4,61</t>
+          <t>1,68; 4,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,96; 4,65</t>
+          <t>1,92; 4,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,79; 2,9</t>
+          <t>0,78; 2,78</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,62; 8,78</t>
+          <t>5,67; 10,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 6,17</t>
+          <t>1,06; 6,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,32</t>
+          <t>0,75; 4,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,61; 5,62</t>
+          <t>0,61; 5,48</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,76; 9,43</t>
+          <t>3,86; 9,37</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,81; 4,12</t>
+          <t>1,84; 4,16</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1,75; 4,02</t>
+          <t>1,73; 4,04</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 2,97</t>
+          <t>1,02; 3,07</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,17; 8,04</t>
+          <t>5,6; 9,46</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,59; 3,38</t>
+          <t>1,57; 3,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,46; 4,75</t>
+          <t>2,37; 4,6</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,14; 2,67</t>
+          <t>1,2; 2,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6,67; 10,29</t>
+          <t>7,11; 10,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,71; 4,24</t>
+          <t>1,65; 4,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,88</t>
+          <t>0,92; 2,74</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,16</t>
+          <t>0,47; 2,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>3,3; 8,47</t>
+          <t>6,47; 9,55</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,94; 3,41</t>
+          <t>1,91; 3,48</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,04; 3,54</t>
+          <t>2,01; 3,56</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,13</t>
+          <t>1,02; 2,16</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>4,99; 8,63</t>
+          <t>7,24; 9,82</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,69%</t>
         </is>
       </c>
     </row>
@@ -1277,47 +1277,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,85; 4,62</t>
+          <t>1,06; 4,79</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,78; 3,05</t>
+          <t>0,79; 3,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,88; 3,24</t>
+          <t>0,9; 3,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3,18; 7,39</t>
+          <t>3,2; 6,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,23</t>
+          <t>0,83; 3,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,01; 4,57</t>
+          <t>2,09; 4,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,4</t>
+          <t>0,56; 2,63</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,91; 7,06</t>
+          <t>4,95; 7,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,05</t>
+          <t>1,1; 3,16</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1327,19 +1327,19 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 2,33</t>
+          <t>0,9; 2,38</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,23; 6,63</t>
+          <t>4,66; 6,91</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,67; 4,11</t>
+          <t>0,66; 4,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,78</t>
+          <t>1,05; 4,76</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,05</t>
+          <t>0,0; 2,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>0,0; 2,07</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,02; 3,96</t>
+          <t>2,04; 3,83</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,74; 2,26</t>
+          <t>0,67; 2,16</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,74; 4,0</t>
+          <t>1,78; 4,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>6,25; 9,57</t>
+          <t>6,18; 9,28</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,89; 3,45</t>
+          <t>1,9; 3,55</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,27</t>
+          <t>0,88; 2,34</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,57; 3,2</t>
+          <t>1,55; 3,3</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,8; 7,41</t>
+          <t>4,85; 7,25</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,81%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,27; 3,43</t>
+          <t>2,29; 3,44</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,5; 3,69</t>
+          <t>2,48; 3,67</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,23; 2,13</t>
+          <t>1,21; 2,05</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5,61; 8,31</t>
+          <t>6,97; 8,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,99; 3,19</t>
+          <t>2,02; 3,12</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,53; 2,5</t>
+          <t>1,47; 2,4</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,36; 2,31</t>
+          <t>1,38; 2,35</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,97; 8,22</t>
+          <t>7,01; 8,61</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,29; 3,11</t>
+          <t>2,25; 3,1</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,11; 2,89</t>
+          <t>2,14; 2,9</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,42; 2,07</t>
+          <t>1,39; 2,07</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>6,21; 7,93</t>
+          <t>7,28; 8,43</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52583</t>
+          <t>53560</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>49196</t>
+          <t>54300</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>101779</t>
+          <t>107860</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>14637; 34328</t>
+          <t>15209; 34730</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6208; 21700</t>
+          <t>7001; 21103</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3549; 14728</t>
+          <t>3180; 14046</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>39469; 68802</t>
+          <t>40336; 71429</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>3741; 16387</t>
+          <t>3966; 15907</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2027; 14601</t>
+          <t>2059; 14149</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3176; 14870</t>
+          <t>3134; 14723</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>39676; 61082</t>
+          <t>43069; 67485</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>21871; 44027</t>
+          <t>22232; 45537</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>11221; 29107</t>
+          <t>10403; 28458</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8628; 24292</t>
+          <t>8945; 24454</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>85463; 121165</t>
+          <t>90446; 127491</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>46397</t>
+          <t>49803</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>31636</t>
+          <t>34724</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>78034</t>
+          <t>84527</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3827; 17778</t>
+          <t>3917; 17882</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11298; 30997</t>
+          <t>12570; 31319</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1070; 11623</t>
+          <t>1520; 11735</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34331; 61296</t>
+          <t>35984; 64100</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3380; 16251</t>
+          <t>3862; 16695</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2543; 12378</t>
+          <t>2870; 12566</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2039; 11680</t>
+          <t>2047; 12527</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22963; 41247</t>
+          <t>25065; 44448</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9837; 27793</t>
+          <t>9300; 28036</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17091; 38245</t>
+          <t>16532; 38508</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4426; 17879</t>
+          <t>4659; 17949</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>64175; 94744</t>
+          <t>69637; 104932</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33703</t>
+          <t>37180</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10223</t>
+          <t>11336</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>43926</t>
+          <t>48516</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8763; 24982</t>
+          <t>9098; 23861</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>12322; 29248</t>
+          <t>12103; 29453</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4145; 15154</t>
+          <t>4083; 14529</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10857; 58661</t>
+          <t>26763; 50995</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1538; 10356</t>
+          <t>1780; 10197</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1975; 11238</t>
+          <t>1964; 12131</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1008; 9344</t>
+          <t>1017; 9110</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>6271; 15733</t>
+          <t>7234; 17565</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12858; 29269</t>
+          <t>13042; 29509</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15558; 35733</t>
+          <t>15387; 35900</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>6977; 20405</t>
+          <t>7004; 21152</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18107; 67124</t>
+          <t>36902; 62352</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>85957</t>
+          <t>99466</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>60910</t>
+          <t>68222</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>146867</t>
+          <t>167688</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>19748; 41818</t>
+          <t>19419; 43292</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28529; 55070</t>
+          <t>27470; 53357</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>13126; 30680</t>
+          <t>13744; 31641</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>69045; 106440</t>
+          <t>80462; 119462</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>12222; 30259</t>
+          <t>11795; 32295</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>7164; 22063</t>
+          <t>7045; 20973</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4221; 17863</t>
+          <t>3859; 16619</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>32294; 82808</t>
+          <t>55756; 82204</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>37974; 66652</t>
+          <t>37382; 67997</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>39292; 68258</t>
+          <t>38717; 68559</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>20432; 42171</t>
+          <t>20131; 42644</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>100495; 173796</t>
+          <t>144357; 195630</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>24503</t>
+          <t>27172</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>46726</t>
+          <t>52452</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>71229</t>
+          <t>79625</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2988; 16193</t>
+          <t>3707; 16789</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3990; 15592</t>
+          <t>4042; 17216</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5467; 20081</t>
+          <t>5570; 20622</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15099; 35107</t>
+          <t>18179; 38553</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4194; 18374</t>
+          <t>4709; 18183</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15335; 34779</t>
+          <t>15895; 35247</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>4304; 17750</t>
+          <t>4110; 19421</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>32876; 59380</t>
+          <t>41095; 64049</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>10410; 28062</t>
+          <t>10092; 29084</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>22473; 45786</t>
+          <t>22570; 45752</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12312; 31671</t>
+          <t>12239; 32305</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>55687; 87257</t>
+          <t>65173; 96639</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1025</t>
+          <t>940</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>58853</t>
+          <t>63614</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>59878</t>
+          <t>64554</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2005; 12254</t>
+          <t>1958; 12262</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2037; 12746</t>
+          <t>2792; 12712</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 5897</t>
+          <t>0; 6098</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 5533</t>
+          <t>0; 4919</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>25259; 49459</t>
+          <t>25461; 47871</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>8252; 25037</t>
+          <t>7429; 24006</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18867; 43318</t>
+          <t>19208; 43355</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>47597; 72875</t>
+          <t>52215; 78361</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>29196; 53393</t>
+          <t>29461; 54949</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>13046; 31256</t>
+          <t>12155; 32248</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>21454; 43811</t>
+          <t>21218; 45219</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>48062; 74242</t>
+          <t>52425; 78462</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>244168</t>
+          <t>268121</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>257545</t>
+          <t>284649</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>501713</t>
+          <t>552770</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>74127; 112167</t>
+          <t>74921; 112407</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>85395; 126289</t>
+          <t>84884; 125608</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>41756; 72116</t>
+          <t>40923; 69266</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>189491; 280392</t>
+          <t>239779; 303141</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>67098; 107651</t>
+          <t>68272; 105476</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>54143; 88656</t>
+          <t>52159; 85047</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>48174; 81501</t>
+          <t>48688; 83146</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>213748; 294043</t>
+          <t>255020; 313081</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>152203; 206449</t>
+          <t>149770; 206136</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>146785; 201203</t>
+          <t>149364; 202008</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>98304; 143298</t>
+          <t>96240; 142950</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>431903; 551416</t>
+          <t>515114; 596594</t>
         </is>
       </c>
     </row>
